--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Martin_2023_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Martin_2023_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{BF05914F-91D3-8145-AA4E-915C6176DF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B391C84F-4E16-4CAF-ACBF-856D1AE88AB3}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -761,7 +761,7 @@
         </row>
         <row r="19">
           <cell r="C19">
-            <v>0.8</v>
+            <v>1.7</v>
           </cell>
         </row>
         <row r="21">
@@ -806,12 +806,12 @@
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1282</v>
+            <v>1371</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>480</v>
+            <v>523</v>
           </cell>
         </row>
       </sheetData>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C18" s="2">
         <f>[1]Inputs!C19</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C32" s="2">
         <f>[1]Inputs!C33</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C33" s="2">
         <f>[1]Inputs!C34</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -8443,15 +8443,15 @@
       </c>
       <c r="B6" s="11">
         <f>Inputs!$C$32*Inputs!$C$6</f>
-        <v>1153.8</v>
+        <v>1233.9000000000001</v>
       </c>
       <c r="C6" s="11">
         <f>Inputs!$C$32*Inputs!$C$6</f>
-        <v>1153.8</v>
+        <v>1233.9000000000001</v>
       </c>
       <c r="D6" s="11">
         <f>Inputs!$C$32*Inputs!$C$6</f>
-        <v>1153.8</v>
+        <v>1233.9000000000001</v>
       </c>
       <c r="E6" s="11">
         <v>135</v>
@@ -8464,15 +8464,15 @@
       </c>
       <c r="H6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>432</v>
+        <v>470.7</v>
       </c>
       <c r="I6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>432</v>
+        <v>470.7</v>
       </c>
       <c r="J6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>432</v>
+        <v>470.7</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>37</v>
@@ -11422,15 +11422,15 @@
       </c>
       <c r="B109" s="29">
         <f t="shared" ref="B109:J109" si="26">B91/B5*B6</f>
-        <v>39.344579999999993</v>
+        <v>42.075990000000004</v>
       </c>
       <c r="C109" s="29">
         <f t="shared" si="26"/>
-        <v>39.344579999999993</v>
+        <v>42.075990000000004</v>
       </c>
       <c r="D109" s="29">
         <f t="shared" si="26"/>
-        <v>39.344579999999993</v>
+        <v>42.075990000000004</v>
       </c>
       <c r="E109" s="29">
         <f t="shared" si="26"/>
@@ -11446,15 +11446,15 @@
       </c>
       <c r="H109" s="29">
         <f t="shared" si="26"/>
-        <v>14.731200000000003</v>
+        <v>16.050870000000003</v>
       </c>
       <c r="I109" s="29">
         <f t="shared" si="26"/>
-        <v>14.731200000000003</v>
+        <v>16.050870000000003</v>
       </c>
       <c r="J109" s="29">
         <f t="shared" si="26"/>
-        <v>14.731200000000003</v>
+        <v>16.050870000000003</v>
       </c>
       <c r="K109" s="5" t="s">
         <v>34</v>
@@ -11469,15 +11469,15 @@
       </c>
       <c r="B111" s="29">
         <f t="shared" ref="B111:J111" si="27">B98-B87-B90+B106-B88+B107-B91+B109</f>
-        <v>58.337701175127883</v>
+        <v>61.069111175127894</v>
       </c>
       <c r="C111" s="29">
         <f t="shared" si="27"/>
-        <v>60.372701972355991</v>
+        <v>63.104111972356002</v>
       </c>
       <c r="D111" s="29">
         <f t="shared" si="27"/>
-        <v>56.544999117058644</v>
+        <v>59.276409117058655</v>
       </c>
       <c r="E111" s="29">
         <f t="shared" si="27"/>
@@ -11493,15 +11493,15 @@
       </c>
       <c r="H111" s="29">
         <f t="shared" si="27"/>
-        <v>19.719158446813047</v>
+        <v>21.038828446813049</v>
       </c>
       <c r="I111" s="29">
         <f t="shared" si="27"/>
-        <v>20.257184592642467</v>
+        <v>21.576854592642469</v>
       </c>
       <c r="J111" s="29">
         <f t="shared" si="27"/>
-        <v>19.212705526556519</v>
+        <v>20.532375526556518</v>
       </c>
       <c r="K111" s="5" t="s">
         <v>34</v>
@@ -11513,15 +11513,15 @@
       </c>
       <c r="B112" s="40">
         <f t="shared" ref="B112:J112" si="28">B111/3.6</f>
-        <v>16.204916993091079</v>
+        <v>16.96364199309108</v>
       </c>
       <c r="C112" s="40">
         <f t="shared" si="28"/>
-        <v>16.770194992321109</v>
+        <v>17.528919992321111</v>
       </c>
       <c r="D112" s="40">
         <f t="shared" si="28"/>
-        <v>15.706944199182956</v>
+        <v>16.465669199182958</v>
       </c>
       <c r="E112" s="40">
         <f t="shared" si="28"/>
@@ -11537,15 +11537,15 @@
       </c>
       <c r="H112" s="40">
         <f t="shared" si="28"/>
-        <v>5.4775440130036239</v>
+        <v>5.8441190130036249</v>
       </c>
       <c r="I112" s="40">
         <f t="shared" si="28"/>
-        <v>5.6269957201784626</v>
+        <v>5.9935707201784636</v>
       </c>
       <c r="J112" s="40">
         <f t="shared" si="28"/>
-        <v>5.3368626462656996</v>
+        <v>5.7034376462656988</v>
       </c>
       <c r="K112" s="5" t="s">
         <v>94</v>
@@ -11557,15 +11557,15 @@
       </c>
       <c r="B113" s="40">
         <f>B112*Inputs!$C$14 / 100</f>
-        <v>5.6214208852353238</v>
+        <v>5.8846195528353249</v>
       </c>
       <c r="C113" s="40">
         <f>C112*Inputs!$C$14 / 100</f>
-        <v>5.8175135620562237</v>
+        <v>6.0807122296562248</v>
       </c>
       <c r="D113" s="40">
         <f>D112*Inputs!$C$14 / 100</f>
-        <v>5.4486761149197722</v>
+        <v>5.7118747825197724</v>
       </c>
       <c r="E113" s="40">
         <f>E112*Inputs!$C$14 / 100</f>
@@ -11581,15 +11581,15 @@
       </c>
       <c r="H113" s="40">
         <f>H112*Inputs!$C$14 / 100</f>
-        <v>1.9001381079349053</v>
+        <v>2.0273015091349058</v>
       </c>
       <c r="I113" s="40">
         <f>I112*Inputs!$C$14 / 100</f>
-        <v>1.9519823073470284</v>
+        <v>2.0791457085470286</v>
       </c>
       <c r="J113" s="40">
         <f>J112*Inputs!$C$14 / 100</f>
-        <v>1.8513363045389863</v>
+        <v>1.9784997057389861</v>
       </c>
       <c r="K113" s="5" t="s">
         <v>95</v>
@@ -11810,15 +11810,15 @@
       </c>
       <c r="B6" s="11">
         <f>Inputs!$C$32*Inputs!$C$6</f>
-        <v>1153.8</v>
+        <v>1233.9000000000001</v>
       </c>
       <c r="C6" s="11">
         <f>Inputs!$C$32*Inputs!$C$6</f>
-        <v>1153.8</v>
+        <v>1233.9000000000001</v>
       </c>
       <c r="D6" s="11">
         <f>Inputs!$C$32*Inputs!$C$6</f>
-        <v>1153.8</v>
+        <v>1233.9000000000001</v>
       </c>
       <c r="E6" s="11">
         <v>135</v>
@@ -11831,15 +11831,15 @@
       </c>
       <c r="H6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>432</v>
+        <v>470.7</v>
       </c>
       <c r="I6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>432</v>
+        <v>470.7</v>
       </c>
       <c r="J6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>432</v>
+        <v>470.7</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>37</v>
@@ -14789,15 +14789,15 @@
       </c>
       <c r="B109" s="29">
         <f t="shared" ref="B109:J109" si="26">B91/B5*B6</f>
-        <v>39.344579999999993</v>
+        <v>42.075990000000004</v>
       </c>
       <c r="C109" s="29">
         <f t="shared" si="26"/>
-        <v>39.344579999999993</v>
+        <v>42.075990000000004</v>
       </c>
       <c r="D109" s="29">
         <f t="shared" si="26"/>
-        <v>39.344579999999993</v>
+        <v>42.075990000000004</v>
       </c>
       <c r="E109" s="29">
         <f t="shared" si="26"/>
@@ -14813,15 +14813,15 @@
       </c>
       <c r="H109" s="29">
         <f t="shared" si="26"/>
-        <v>14.731200000000003</v>
+        <v>16.050870000000003</v>
       </c>
       <c r="I109" s="29">
         <f t="shared" si="26"/>
-        <v>14.731200000000003</v>
+        <v>16.050870000000003</v>
       </c>
       <c r="J109" s="29">
         <f t="shared" si="26"/>
-        <v>14.731200000000003</v>
+        <v>16.050870000000003</v>
       </c>
       <c r="K109" s="5" t="s">
         <v>34</v>
@@ -14836,15 +14836,15 @@
       </c>
       <c r="B111" s="29">
         <f t="shared" ref="B111:J111" si="27">B98-B87-B90+B106-B88+B107-B91+B109</f>
-        <v>58.413539165211802</v>
+        <v>61.144949165211813</v>
       </c>
       <c r="C111" s="29">
         <f t="shared" si="27"/>
-        <v>60.448539962439909</v>
+        <v>63.17994996243992</v>
       </c>
       <c r="D111" s="29">
         <f t="shared" si="27"/>
-        <v>56.620837107142563</v>
+        <v>59.352247107142574</v>
       </c>
       <c r="E111" s="29">
         <f t="shared" si="27"/>
@@ -14860,15 +14860,15 @@
       </c>
       <c r="H111" s="29">
         <f t="shared" si="27"/>
-        <v>19.757077441855003</v>
+        <v>21.076747441855005</v>
       </c>
       <c r="I111" s="29">
         <f t="shared" si="27"/>
-        <v>20.295103587684427</v>
+        <v>21.614773587684425</v>
       </c>
       <c r="J111" s="29">
         <f t="shared" si="27"/>
-        <v>19.250624521598475</v>
+        <v>20.570294521598477</v>
       </c>
       <c r="K111" s="5" t="s">
         <v>34</v>
@@ -14880,15 +14880,15 @@
       </c>
       <c r="B112" s="40">
         <f t="shared" ref="B112:J112" si="28">B111/3.6</f>
-        <v>16.225983101447721</v>
+        <v>16.984708101447726</v>
       </c>
       <c r="C112" s="40">
         <f t="shared" si="28"/>
-        <v>16.791261100677751</v>
+        <v>17.549986100677756</v>
       </c>
       <c r="D112" s="40">
         <f t="shared" si="28"/>
-        <v>15.7280103075396</v>
+        <v>16.486735307539604</v>
       </c>
       <c r="E112" s="40">
         <f t="shared" si="28"/>
@@ -14904,15 +14904,15 @@
       </c>
       <c r="H112" s="40">
         <f t="shared" si="28"/>
-        <v>5.488077067181945</v>
+        <v>5.854652067181946</v>
       </c>
       <c r="I112" s="40">
         <f t="shared" si="28"/>
-        <v>5.6375287743567855</v>
+        <v>6.0041037743567847</v>
       </c>
       <c r="J112" s="40">
         <f t="shared" si="28"/>
-        <v>5.3473957004440207</v>
+        <v>5.7139707004440217</v>
       </c>
       <c r="K112" s="5" t="s">
         <v>94</v>
@@ -14924,15 +14924,15 @@
       </c>
       <c r="B113" s="40">
         <f>B112*Inputs!$C$14 / 100</f>
-        <v>5.6287286339598097</v>
+        <v>5.8919273015598117</v>
       </c>
       <c r="C113" s="40">
         <f>C112*Inputs!$C$14 / 100</f>
-        <v>5.8248213107807096</v>
+        <v>6.0880199783807116</v>
       </c>
       <c r="D113" s="40">
         <f>D112*Inputs!$C$14 / 100</f>
-        <v>5.4559838636442581</v>
+        <v>5.7191825312442601</v>
       </c>
       <c r="E113" s="40">
         <f>E112*Inputs!$C$14 / 100</f>
@@ -14948,15 +14948,15 @@
       </c>
       <c r="H113" s="40">
         <f>H112*Inputs!$C$14 / 100</f>
-        <v>1.9037919822971483</v>
+        <v>2.0309553834971488</v>
       </c>
       <c r="I113" s="40">
         <f>I112*Inputs!$C$14 / 100</f>
-        <v>1.9556361817092718</v>
+        <v>2.0827995829092716</v>
       </c>
       <c r="J113" s="40">
         <f>J112*Inputs!$C$14 / 100</f>
-        <v>1.8549901789012293</v>
+        <v>1.9821535801012298</v>
       </c>
       <c r="K113" s="5" t="s">
         <v>95</v>
@@ -15052,11 +15052,11 @@
       </c>
       <c r="E3" s="41">
         <f>AVERAGE('CO2 Price Corrected LCOF'!B113:D113)</f>
-        <v>5.6292035207371072</v>
+        <v>5.8924021883371074</v>
       </c>
       <c r="F3" s="41">
         <f>AVERAGE('WACC Corrected LCOF'!B113:D113)</f>
-        <v>5.6365112694615931</v>
+        <v>5.8997099370615942</v>
       </c>
       <c r="H3" s="35" t="s">
         <v>100</v>
@@ -15074,11 +15074,11 @@
       </c>
       <c r="L3" s="41">
         <f>AVERAGE('CO2 Price Corrected LCOF'!H113:J113)</f>
-        <v>1.9011522399403067</v>
+        <v>2.0283156411403067</v>
       </c>
       <c r="M3" s="41">
         <f>AVERAGE('WACC Corrected LCOF'!H113:J113)</f>
-        <v>1.9048061143025496</v>
+        <v>2.0319695155025497</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15098,11 +15098,11 @@
       </c>
       <c r="E4" s="37">
         <f>E3/Inputs!$C$6</f>
-        <v>6.2546705785967855</v>
+        <v>6.5471135425967857</v>
       </c>
       <c r="F4" s="37">
         <f>F3/Inputs!$C$6</f>
-        <v>6.2627902994017699</v>
+        <v>6.5552332634017709</v>
       </c>
       <c r="H4" s="35" t="s">
         <v>100</v>
@@ -15120,11 +15120,11 @@
       </c>
       <c r="L4" s="37">
         <f>L3/Inputs!$C$6</f>
-        <v>2.112391377711452</v>
+        <v>2.2536840457114518</v>
       </c>
       <c r="M4" s="37">
         <f>M3/Inputs!$C$6</f>
-        <v>2.1164512381139442</v>
+        <v>2.2577439061139439</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15158,19 +15158,19 @@
       </c>
       <c r="J5" s="37">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="K5" s="37">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="L5" s="37">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="M5" s="37">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15366,11 +15366,11 @@
       </c>
       <c r="E10" s="36">
         <f>(E4-E5) / E9 * 10^6</f>
-        <v>2088.2104236057571</v>
+        <v>2200.1663037887292</v>
       </c>
       <c r="F10" s="36">
         <f>(F4-F5) / F9 * 10^6</f>
-        <v>2091.3188946632522</v>
+        <v>2203.2747748462243</v>
       </c>
       <c r="H10" s="35" t="s">
         <v>107</v>
@@ -15380,19 +15380,19 @@
       </c>
       <c r="J10" s="36">
         <f>(J4-J5) / J9 * 10^6</f>
-        <v>205.40678396356506</v>
+        <v>-139.14003223090702</v>
       </c>
       <c r="K10" s="36">
         <f>(K4-K5) / K9 * 10^6</f>
-        <v>10.431638901904449</v>
+        <v>-334.11517729256764</v>
       </c>
       <c r="L10" s="36">
         <f>(L4-L5) / L9 * 10^6</f>
-        <v>502.42252310173075</v>
+        <v>211.96675014172808</v>
       </c>
       <c r="M10" s="36">
         <f>(M4-M5) / M9 * 10^6</f>
-        <v>503.97675863047817</v>
+        <v>213.52098567047554</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C15" s="44">
         <f>C14*Inputs!$C$32 * 10^-6</f>
-        <v>0.59592570048000004</v>
+        <v>0.63729651744000004</v>
       </c>
       <c r="H15" s="43" t="s">
         <v>110</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="J15" s="44">
         <f>J14*Inputs!$C$32 * 10^-6</f>
-        <v>0.59592570048000004</v>
+        <v>0.63729651744000004</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="C16" s="44">
         <f>F4+C15</f>
-        <v>6.8587159998817704</v>
+        <v>7.1925297808417712</v>
       </c>
       <c r="H16" s="43" t="s">
         <v>111</v>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="J16" s="44">
         <f>M4+J15</f>
-        <v>2.7123769385939442</v>
+        <v>2.8950404235539438</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="C17" s="2">
         <f>(C16-C5) /C9 * 10^6</f>
-        <v>2319.4570088730798</v>
+        <v>2447.2508704637544</v>
       </c>
       <c r="H17" s="43" t="s">
         <v>112</v>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="J17" s="2">
         <f>(J16-J5) /J9 * 10^6</f>
-        <v>732.11487284030557</v>
+        <v>457.49708128800529</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Martin_2023_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Martin_2023_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{BF05914F-91D3-8145-AA4E-915C6176DF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B391C84F-4E16-4CAF-ACBF-856D1AE88AB3}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -811,7 +811,7 @@
         </row>
         <row r="34">
           <cell r="C34">
-            <v>523</v>
+            <v>497</v>
           </cell>
         </row>
       </sheetData>
@@ -1159,9 +1159,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C33" s="2">
         <f>[1]Inputs!C34</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1544,18 +1544,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P114"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="31.5" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="8.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.75" style="5" customWidth="1"/>
-    <col min="12" max="12" width="8.75" style="4" customWidth="1"/>
+    <col min="4" max="10" width="8.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.69921875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="8.69921875" style="4" customWidth="1"/>
     <col min="13" max="13" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.19921875" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.75" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="8.75" style="4"/>
+    <col min="16" max="16" width="8.69921875" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="8.69921875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4893,18 +4893,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P113"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="31.5" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="8.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.75" style="5" customWidth="1"/>
-    <col min="12" max="12" width="8.75" style="4" customWidth="1"/>
+    <col min="4" max="10" width="8.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.69921875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="8.69921875" style="4" customWidth="1"/>
     <col min="13" max="13" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.19921875" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.75" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="8.75" style="4"/>
+    <col min="16" max="16" width="8.69921875" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="8.69921875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -8245,18 +8245,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P113"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="31.5" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="8.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.75" style="5" customWidth="1"/>
-    <col min="12" max="12" width="8.75" style="4" customWidth="1"/>
+    <col min="4" max="10" width="8.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.69921875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="8.69921875" style="4" customWidth="1"/>
     <col min="13" max="13" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.19921875" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.75" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="8.75" style="4"/>
+    <col min="16" max="16" width="8.69921875" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="8.69921875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -8464,15 +8464,15 @@
       </c>
       <c r="H6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>470.7</v>
+        <v>447.3</v>
       </c>
       <c r="I6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>470.7</v>
+        <v>447.3</v>
       </c>
       <c r="J6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>470.7</v>
+        <v>447.3</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>37</v>
@@ -11446,15 +11446,15 @@
       </c>
       <c r="H109" s="29">
         <f t="shared" si="26"/>
-        <v>16.050870000000003</v>
+        <v>15.252930000000003</v>
       </c>
       <c r="I109" s="29">
         <f t="shared" si="26"/>
-        <v>16.050870000000003</v>
+        <v>15.252930000000003</v>
       </c>
       <c r="J109" s="29">
         <f t="shared" si="26"/>
-        <v>16.050870000000003</v>
+        <v>15.252930000000003</v>
       </c>
       <c r="K109" s="5" t="s">
         <v>34</v>
@@ -11493,15 +11493,15 @@
       </c>
       <c r="H111" s="29">
         <f t="shared" si="27"/>
-        <v>21.038828446813049</v>
+        <v>20.240888446813045</v>
       </c>
       <c r="I111" s="29">
         <f t="shared" si="27"/>
-        <v>21.576854592642469</v>
+        <v>20.778914592642469</v>
       </c>
       <c r="J111" s="29">
         <f t="shared" si="27"/>
-        <v>20.532375526556518</v>
+        <v>19.734435526556517</v>
       </c>
       <c r="K111" s="5" t="s">
         <v>34</v>
@@ -11537,15 +11537,15 @@
       </c>
       <c r="H112" s="40">
         <f t="shared" si="28"/>
-        <v>5.8441190130036249</v>
+        <v>5.6224690130036237</v>
       </c>
       <c r="I112" s="40">
         <f t="shared" si="28"/>
-        <v>5.9935707201784636</v>
+        <v>5.7719207201784632</v>
       </c>
       <c r="J112" s="40">
         <f t="shared" si="28"/>
-        <v>5.7034376462656988</v>
+        <v>5.4817876462656994</v>
       </c>
       <c r="K112" s="5" t="s">
         <v>94</v>
@@ -11581,15 +11581,15 @@
       </c>
       <c r="H113" s="40">
         <f>H112*Inputs!$C$14 / 100</f>
-        <v>2.0273015091349058</v>
+        <v>1.9504120107349052</v>
       </c>
       <c r="I113" s="40">
         <f>I112*Inputs!$C$14 / 100</f>
-        <v>2.0791457085470286</v>
+        <v>2.0022562101470287</v>
       </c>
       <c r="J113" s="40">
         <f>J112*Inputs!$C$14 / 100</f>
-        <v>1.9784997057389861</v>
+        <v>1.9016102073389862</v>
       </c>
       <c r="K113" s="5" t="s">
         <v>95</v>
@@ -11603,18 +11603,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P113"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="31.5" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="8.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.75" style="5" customWidth="1"/>
-    <col min="12" max="12" width="8.75" style="4" customWidth="1"/>
+    <col min="4" max="10" width="8.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.69921875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="8.69921875" style="4" customWidth="1"/>
     <col min="13" max="13" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.19921875" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.75" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="8.75" style="4"/>
+    <col min="16" max="16" width="8.69921875" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="8.69921875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -11831,15 +11831,15 @@
       </c>
       <c r="H6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>470.7</v>
+        <v>447.3</v>
       </c>
       <c r="I6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>470.7</v>
+        <v>447.3</v>
       </c>
       <c r="J6" s="11">
         <f>Inputs!$C$33*Inputs!$C$6</f>
-        <v>470.7</v>
+        <v>447.3</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>37</v>
@@ -14813,15 +14813,15 @@
       </c>
       <c r="H109" s="29">
         <f t="shared" si="26"/>
-        <v>16.050870000000003</v>
+        <v>15.252930000000003</v>
       </c>
       <c r="I109" s="29">
         <f t="shared" si="26"/>
-        <v>16.050870000000003</v>
+        <v>15.252930000000003</v>
       </c>
       <c r="J109" s="29">
         <f t="shared" si="26"/>
-        <v>16.050870000000003</v>
+        <v>15.252930000000003</v>
       </c>
       <c r="K109" s="5" t="s">
         <v>34</v>
@@ -14860,15 +14860,15 @@
       </c>
       <c r="H111" s="29">
         <f t="shared" si="27"/>
-        <v>21.076747441855005</v>
+        <v>20.278807441855005</v>
       </c>
       <c r="I111" s="29">
         <f t="shared" si="27"/>
-        <v>21.614773587684425</v>
+        <v>20.816833587684428</v>
       </c>
       <c r="J111" s="29">
         <f t="shared" si="27"/>
-        <v>20.570294521598477</v>
+        <v>19.772354521598473</v>
       </c>
       <c r="K111" s="5" t="s">
         <v>34</v>
@@ -14904,15 +14904,15 @@
       </c>
       <c r="H112" s="40">
         <f t="shared" si="28"/>
-        <v>5.854652067181946</v>
+        <v>5.6330020671819456</v>
       </c>
       <c r="I112" s="40">
         <f t="shared" si="28"/>
-        <v>6.0041037743567847</v>
+        <v>5.7824537743567852</v>
       </c>
       <c r="J112" s="40">
         <f t="shared" si="28"/>
-        <v>5.7139707004440217</v>
+        <v>5.4923207004440204</v>
       </c>
       <c r="K112" s="5" t="s">
         <v>94</v>
@@ -14948,15 +14948,15 @@
       </c>
       <c r="H113" s="40">
         <f>H112*Inputs!$C$14 / 100</f>
-        <v>2.0309553834971488</v>
+        <v>1.9540658850971484</v>
       </c>
       <c r="I113" s="40">
         <f>I112*Inputs!$C$14 / 100</f>
-        <v>2.0827995829092716</v>
+        <v>2.0059100845092717</v>
       </c>
       <c r="J113" s="40">
         <f>J112*Inputs!$C$14 / 100</f>
-        <v>1.9821535801012298</v>
+        <v>1.9052640817012292</v>
       </c>
       <c r="K113" s="5" t="s">
         <v>95</v>
@@ -14970,13 +14970,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -15074,11 +15074,11 @@
       </c>
       <c r="L3" s="41">
         <f>AVERAGE('CO2 Price Corrected LCOF'!H113:J113)</f>
-        <v>2.0283156411403067</v>
+        <v>1.951426142740307</v>
       </c>
       <c r="M3" s="41">
         <f>AVERAGE('WACC Corrected LCOF'!H113:J113)</f>
-        <v>2.0319695155025497</v>
+        <v>1.95508001710255</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15120,11 +15120,11 @@
       </c>
       <c r="L4" s="37">
         <f>L3/Inputs!$C$6</f>
-        <v>2.2536840457114518</v>
+        <v>2.168251269711452</v>
       </c>
       <c r="M4" s="37">
         <f>M3/Inputs!$C$6</f>
-        <v>2.2577439061139439</v>
+        <v>2.1723111301139442</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15388,11 +15388,11 @@
       </c>
       <c r="L10" s="36">
         <f>(L4-L5) / L9 * 10^6</f>
-        <v>211.96675014172808</v>
+        <v>179.26053795344427</v>
       </c>
       <c r="M10" s="36">
         <f>(M4-M5) / M9 * 10^6</f>
-        <v>213.52098567047554</v>
+        <v>180.81477348219173</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="J16" s="44">
         <f>M4+J15</f>
-        <v>2.8950404235539438</v>
+        <v>2.8096076475539444</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="J17" s="2">
         <f>(J16-J5) /J9 * 10^6</f>
-        <v>457.49708128800529</v>
+        <v>424.7908690997217</v>
       </c>
     </row>
   </sheetData>
